--- a/data/employees/EMP028/AST-EMP028-06.xlsx
+++ b/data/employees/EMP028/AST-EMP028-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Budget Tracker - Jamie Brown (Finance)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Jamie Brown | Role: Analyst | Location: Bengaluru | Date: 2025-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>68</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Cost Centre</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Budget ($K)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Actual ($K)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Variance ($K)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Variance %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CC-1001 Engineering</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2380</v>
-      </c>
-      <c r="D5" t="n">
-        <v>120</v>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>4.8</v>
+        <v>75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Fabric semantic model planning. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CC-1002 Operations</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1920</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-120</v>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>-6.7</v>
+        <v>68</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Section 1: Operational risk review. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CC-1003 R&amp;D</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100</v>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
+        <v>84</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Section 1: Operational risk review. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CC-1004 IT</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1195</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>94</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>On Track</t>
+          <t>Section 1: Fabric semantic model planning. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>62</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>62</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>86</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>82</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>82</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>68</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>88</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>66</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>90</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>70</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>99</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>70</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>65</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>76</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>72</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>74</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp028 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>94</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP028</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP028 contributes to ast emp028 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>